--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.90 seconds</t>
+    <t>129.93 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.93 seconds</t>
+    <t>130.12 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>130.12 seconds</t>
+    <t>128.34 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.34 seconds</t>
+    <t>127.35 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.35 seconds</t>
+    <t>126.76 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.76 seconds</t>
+    <t>130.32 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>130.32 seconds</t>
+    <t>127.75 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.75 seconds</t>
+    <t>128.97 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.97 seconds</t>
+    <t>128.12 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.12 seconds</t>
+    <t>127.23 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.23 seconds</t>
+    <t>126.96 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.96 seconds</t>
+    <t>127.43 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.43 seconds</t>
+    <t>129.31 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.31 seconds</t>
+    <t>126.15 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.15 seconds</t>
+    <t>129.06 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.06 seconds</t>
+    <t>126.81 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.81 seconds</t>
+    <t>129.16 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.16 seconds</t>
+    <t>127.25 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.25 seconds</t>
+    <t>126.59 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.59 seconds</t>
+    <t>127.83 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.83 seconds</t>
+    <t>126.62 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.62 seconds</t>
+    <t>127.10 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.10 seconds</t>
+    <t>127.44 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.44 seconds</t>
+    <t>127.59 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.59 seconds</t>
+    <t>129.19 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.19 seconds</t>
+    <t>128.56 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.56 seconds</t>
+    <t>128.28 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.28 seconds</t>
+    <t>129.57 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.57 seconds</t>
+    <t>127.70 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.70 seconds</t>
+    <t>127.11 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.11 seconds</t>
+    <t>129.27 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.27 seconds</t>
+    <t>125.96 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>125.96 seconds</t>
+    <t>129.53 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.53 seconds</t>
+    <t>128.68 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.68 seconds</t>
+    <t>128.61 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.61 seconds</t>
+    <t>127.75 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.75 seconds</t>
+    <t>126.95 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.95 seconds</t>
+    <t>128.90 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.90 seconds</t>
+    <t>128.15 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>128.15 seconds</t>
+    <t>130.75 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>130.75 seconds</t>
+    <t>125.65 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>125.65 seconds</t>
+    <t>129.70 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.70 seconds</t>
+    <t>127.54 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.54 seconds</t>
+    <t>129.24 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.24 seconds</t>
+    <t>129.75 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>129.75 seconds</t>
+    <t>127.83 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>127.83 seconds</t>
+    <t>126.95 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>126.95 seconds</t>
+    <t>130.31 seconds</t>
   </si>
 </sst>
 </file>

--- a/reports/latest/Excel/Summary_Report.xlsx
+++ b/reports/latest/Excel/Summary_Report.xlsx
@@ -37,7 +37,7 @@
     <t>Run Duration (Overall)</t>
   </si>
   <si>
-    <t>130.31 seconds</t>
+    <t>126.45 seconds</t>
   </si>
 </sst>
 </file>
